--- a/grupos/5APM - Estadisticos 20211.xlsx
+++ b/grupos/5APM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="127">
   <si>
     <t>Materia</t>
   </si>
@@ -161,24 +161,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -194,12 +194,48 @@
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>LADINO</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MOISES URIEL</t>
+  </si>
+  <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>ALEJO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CESPEDES</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
     <t>CHORA</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
     <t>GARIBAY</t>
   </si>
   <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -209,48 +245,78 @@
     <t>HERAS</t>
   </si>
   <si>
-    <t>LADINO</t>
-  </si>
-  <si>
     <t>LICEA</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>RICO</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SERRANO</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>SILVESTRE</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PANZO</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
     <t>CELICEO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
+    <t>CALPULALPAN</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
   </si>
   <si>
     <t>ANDRADE</t>
   </si>
   <si>
+    <t>ALCARAZ</t>
+  </si>
+  <si>
     <t>ORTIZ</t>
   </si>
   <si>
@@ -260,142 +326,76 @@
     <t>HUERTA</t>
   </si>
   <si>
-    <t>MOISES URIEL</t>
+    <t>LLAVE</t>
+  </si>
+  <si>
+    <t>RAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>ERICK MANUEL</t>
+  </si>
+  <si>
+    <t>KARLA FABIOLA</t>
   </si>
   <si>
     <t>GABRIEL ALEJANDRO</t>
   </si>
   <si>
+    <t>IRVING YAHIR</t>
+  </si>
+  <si>
+    <t>BRAULIO VADIR</t>
+  </si>
+  <si>
     <t>MARCOS URIEL</t>
   </si>
   <si>
+    <t>VIANEY</t>
+  </si>
+  <si>
     <t>URIEL</t>
   </si>
   <si>
     <t>PAOLA</t>
   </si>
   <si>
+    <t>YARELY JACQUELINE</t>
+  </si>
+  <si>
     <t>CESAR ENRIQUE</t>
   </si>
   <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
     <t>QADMIEL TAMARA</t>
   </si>
   <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
     <t>ALEXANDER</t>
   </si>
   <si>
+    <t>RENZO JHOVANI</t>
+  </si>
+  <si>
+    <t>MARIA DE JESUS</t>
+  </si>
+  <si>
     <t>NADYA GUADALUPE</t>
   </si>
   <si>
     <t>DANTE GAMALIEL</t>
   </si>
   <si>
+    <t>ANGEL EDUARDO</t>
+  </si>
+  <si>
     <t>ABDIEL ANTONIO</t>
   </si>
   <si>
     <t>DANIELA JAQUELINE</t>
-  </si>
-  <si>
-    <t>ALEJO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CESPEDES</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>ALCARAZ</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
-    <t>RAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>ERICK MANUEL</t>
-  </si>
-  <si>
-    <t>KARLA FABIOLA</t>
-  </si>
-  <si>
-    <t>IRVING YAHIR</t>
-  </si>
-  <si>
-    <t>BRAULIO VADIR</t>
-  </si>
-  <si>
-    <t>VIANEY</t>
-  </si>
-  <si>
-    <t>YARELY JACQUELINE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>RENZO JHOVANI</t>
-  </si>
-  <si>
-    <t>MARIA DE JESUS</t>
-  </si>
-  <si>
-    <t>ANGEL EDUARDO</t>
   </si>
   <si>
     <t>YESUA ISIDRO</t>
@@ -902,16 +902,16 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -941,10 +941,10 @@
         <v>7</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -979,16 +979,16 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1018,13 +1018,13 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -1041,13 +1041,13 @@
         <v>-1</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1059,10 +1059,10 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1095,13 +1095,13 @@
         <v>-1</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -1133,16 +1133,16 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1172,13 +1172,13 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>7</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1210,16 +1210,16 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1255,7 +1255,7 @@
         <v>6</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1272,7 +1272,7 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>6</v>
@@ -1287,16 +1287,16 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1326,7 +1326,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>6</v>
@@ -1364,16 +1364,16 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1400,10 +1400,10 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1441,16 +1441,16 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1480,13 +1480,13 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1518,16 +1518,16 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1557,13 +1557,13 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1580,13 +1580,13 @@
         <v>5</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -1595,16 +1595,16 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1634,13 +1634,13 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -1672,16 +1672,16 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1714,10 +1714,10 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1734,10 +1734,10 @@
         <v>6</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>6</v>
@@ -1749,16 +1749,16 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1788,10 +1788,10 @@
         <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1814,7 +1814,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>8</v>
@@ -1826,16 +1826,16 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1862,16 +1862,16 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>8</v>
@@ -1888,7 +1888,7 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>6</v>
@@ -1903,16 +1903,16 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -1942,7 +1942,7 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>6</v>
@@ -1980,16 +1980,16 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2016,10 +2016,10 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -2039,7 +2039,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -2048,7 +2048,7 @@
         <v>7</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -2057,16 +2057,16 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2093,7 +2093,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>6</v>
@@ -2102,7 +2102,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>-1</v>
@@ -2122,7 +2122,7 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -2134,16 +2134,16 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2170,13 +2170,13 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2199,7 +2199,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E21">
         <v>8</v>
@@ -2211,16 +2211,16 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2247,13 +2247,13 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2288,16 +2288,16 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2324,16 +2324,16 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2350,7 +2350,7 @@
         <v>9</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D23">
         <v>7</v>
@@ -2365,16 +2365,16 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2404,13 +2404,13 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2442,16 +2442,16 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2478,16 +2478,16 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
+        <v>10</v>
+      </c>
+      <c r="V24">
         <v>9</v>
       </c>
-      <c r="V24">
-        <v>8</v>
-      </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2504,13 +2504,13 @@
         <v>5</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>6</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -2519,16 +2519,16 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2555,16 +2555,16 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>5</v>
@@ -2596,16 +2596,16 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2635,13 +2635,13 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>7</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2658,13 +2658,13 @@
         <v>5</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -2673,13 +2673,13 @@
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I27">
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2709,16 +2709,16 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -2735,7 +2735,7 @@
         <v>5</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>7</v>
@@ -2750,16 +2750,16 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2786,10 +2786,10 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>7</v>
@@ -2827,16 +2827,16 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -2863,10 +2863,10 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -2934,7 +2934,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>47</v>
@@ -2943,30 +2943,30 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>65.38</v>
+        <v>69.23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>26.92</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>34.62</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
@@ -2975,25 +2975,25 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>7</v>
       </c>
       <c r="F3">
-        <v>69.23</v>
+        <v>73.08</v>
       </c>
       <c r="G3">
         <v>26.92</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3007,30 +3007,30 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>73.08</v>
+        <v>80.77</v>
       </c>
       <c r="G4">
-        <v>19.23</v>
+        <v>15.38</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>7.69</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>50</v>
@@ -3039,30 +3039,30 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>84.62</v>
+      </c>
+      <c r="G5">
+        <v>15.38</v>
+      </c>
+      <c r="H5">
+        <v>6.7</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>73.08</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>6.8</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>26.92</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>51</v>
@@ -3071,30 +3071,30 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>88.45999999999999</v>
+      </c>
+      <c r="G6">
+        <v>11.54</v>
+      </c>
+      <c r="H6">
+        <v>6.7</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>80.77</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>6.6</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>19.23</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
@@ -3103,19 +3103,19 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>88.45999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="G7">
-        <v>11.54</v>
+        <v>7.69</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3131,7 +3131,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3166,10 +3166,10 @@
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -3180,461 +3180,21 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920224</v>
+        <v>19330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920224</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920224</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920227</v>
-      </c>
-      <c r="B6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920231</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920231</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920231</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920233</v>
-      </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920233</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920234</v>
-      </c>
-      <c r="B12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920235</v>
-      </c>
-      <c r="B13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920236</v>
-      </c>
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920236</v>
-      </c>
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920236</v>
-      </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920237</v>
-      </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051420227</v>
-      </c>
-      <c r="B18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920239</v>
-      </c>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920241</v>
-      </c>
-      <c r="B20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920241</v>
-      </c>
-      <c r="B21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920243</v>
-      </c>
-      <c r="B22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920243</v>
-      </c>
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920243</v>
-      </c>
-      <c r="B24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" t="s">
-        <v>91</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920244</v>
-      </c>
-      <c r="B25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3677,98 +3237,98 @@
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920231</v>
+        <v>19330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920236</v>
+        <v>19330051920223</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920243</v>
+        <v>19330051920430</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920233</v>
+        <v>19330051920225</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920241</v>
+        <v>19330051920226</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3776,129 +3336,129 @@
         <v>19330051920227</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920234</v>
+        <v>19330051920229</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920235</v>
+        <v>19330051920230</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920237</v>
+        <v>19330051920231</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051420227</v>
+        <v>19330051920232</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920239</v>
+        <v>19330051920233</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920244</v>
+        <v>19330051920234</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920223</v>
+        <v>19330051920429</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
         <v>114</v>
@@ -3909,13 +3469,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920430</v>
+        <v>19330051920235</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
         <v>115</v>
@@ -3926,13 +3486,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920225</v>
+        <v>19330051920237</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
         <v>116</v>
@@ -3943,13 +3503,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920226</v>
+        <v>19330051920228</v>
       </c>
       <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
         <v>96</v>
-      </c>
-      <c r="C18" t="s">
-        <v>107</v>
       </c>
       <c r="D18" t="s">
         <v>117</v>
@@ -3960,13 +3520,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920229</v>
+        <v>19330051420227</v>
       </c>
       <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
         <v>97</v>
-      </c>
-      <c r="C19" t="s">
-        <v>65</v>
       </c>
       <c r="D19" t="s">
         <v>118</v>
@@ -3977,13 +3537,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920230</v>
+        <v>19330051920404</v>
       </c>
       <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" t="s">
         <v>98</v>
-      </c>
-      <c r="C20" t="s">
-        <v>108</v>
       </c>
       <c r="D20" t="s">
         <v>119</v>
@@ -3994,13 +3554,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920232</v>
+        <v>19330051920240</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
         <v>120</v>
@@ -4011,13 +3571,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920429</v>
+        <v>19330051920239</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
         <v>121</v>
@@ -4028,13 +3588,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920228</v>
+        <v>19330051920241</v>
       </c>
       <c r="B23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" t="s">
         <v>100</v>
-      </c>
-      <c r="C23" t="s">
-        <v>111</v>
       </c>
       <c r="D23" t="s">
         <v>122</v>
@@ -4045,13 +3605,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920404</v>
+        <v>19330051920242</v>
       </c>
       <c r="B24" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
         <v>123</v>
@@ -4062,13 +3622,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920240</v>
+        <v>19330051920243</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
         <v>124</v>
@@ -4079,13 +3639,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920242</v>
+        <v>19330051920244</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
         <v>125</v>
@@ -4099,10 +3659,10 @@
         <v>19330051920245</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
         <v>126</v>
@@ -4118,7 +3678,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4150,16 +3710,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920235</v>
+        <v>19330051920237</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4173,91 +3733,91 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920235</v>
+        <v>19330051920237</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920227</v>
+        <v>19330051920234</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920234</v>
+        <v>19330051920429</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920429</v>
+        <v>19330051920235</v>
       </c>
       <c r="B6" t="s">
         <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4265,71 +3825,25 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920237</v>
+        <v>19330051920244</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051420227</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920239</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5APM - Estadisticos 20211.xlsx
+++ b/grupos/5APM - Estadisticos 20211.xlsx
@@ -917,7 +917,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1071,7 +1071,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1107,7 +1107,7 @@
         <v>5</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1148,7 +1148,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1184,7 +1184,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1225,7 +1225,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1261,7 +1261,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1302,7 +1302,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1379,7 +1379,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1456,7 +1456,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1533,7 +1533,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1610,7 +1610,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1687,7 +1687,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1764,7 +1764,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1841,7 +1841,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1877,7 +1877,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1918,7 +1918,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1995,7 +1995,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2031,7 +2031,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2072,7 +2072,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2149,7 +2149,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2226,7 +2226,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2262,7 +2262,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2303,7 +2303,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2380,7 +2380,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2416,7 +2416,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2457,7 +2457,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2493,7 +2493,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2534,7 +2534,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2570,7 +2570,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2611,7 +2611,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2647,7 +2647,7 @@
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2688,7 +2688,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2765,7 +2765,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2842,7 +2842,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3083,7 +3083,7 @@
         <v>11.54</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/5APM - Estadisticos 20211.xlsx
+++ b/grupos/5APM - Estadisticos 20211.xlsx
@@ -194,178 +194,178 @@
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>MOISES URIEL</t>
+  </si>
+  <si>
+    <t>ALEJO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CESPEDES</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>CHORA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>GARIBAY</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERAS</t>
+  </si>
+  <si>
     <t>LADINO</t>
   </si>
   <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MOISES URIEL</t>
+    <t>LICEA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>CELICEO</t>
+  </si>
+  <si>
+    <t>CALPULALPAN</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ALCARAZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LLAVE</t>
+  </si>
+  <si>
+    <t>RAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>ERICK MANUEL</t>
+  </si>
+  <si>
+    <t>KARLA FABIOLA</t>
+  </si>
+  <si>
+    <t>GABRIEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IRVING YAHIR</t>
+  </si>
+  <si>
+    <t>BRAULIO VADIR</t>
+  </si>
+  <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
+    <t>VIANEY</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>YARELY JACQUELINE</t>
+  </si>
+  <si>
+    <t>CESAR ENRIQUE</t>
   </si>
   <si>
     <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>ALEJO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CESPEDES</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>CHORA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>GARIBAY</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERAS</t>
-  </si>
-  <si>
-    <t>LICEA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CELICEO</t>
-  </si>
-  <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ALCARAZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
-    <t>RAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>ERICK MANUEL</t>
-  </si>
-  <si>
-    <t>KARLA FABIOLA</t>
-  </si>
-  <si>
-    <t>GABRIEL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IRVING YAHIR</t>
-  </si>
-  <si>
-    <t>BRAULIO VADIR</t>
-  </si>
-  <si>
-    <t>MARCOS URIEL</t>
-  </si>
-  <si>
-    <t>VIANEY</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>YARELY JACQUELINE</t>
-  </si>
-  <si>
-    <t>CESAR ENRIQUE</t>
   </si>
   <si>
     <t>QADMIEL TAMARA</t>
@@ -914,7 +914,7 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -991,7 +991,7 @@
         <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>7</v>
@@ -1027,7 +1027,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -1145,7 +1145,7 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -1222,7 +1222,7 @@
         <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>9</v>
@@ -1376,7 +1376,7 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1453,7 +1453,7 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -1530,7 +1530,7 @@
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>6</v>
@@ -1566,7 +1566,7 @@
         <v>8</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1684,7 +1684,7 @@
         <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -1838,7 +1838,7 @@
         <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -1915,7 +1915,7 @@
         <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>6</v>
@@ -1951,7 +1951,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2051,7 +2051,7 @@
         <v>5</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -2105,7 +2105,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2146,7 +2146,7 @@
         <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>6</v>
@@ -2182,7 +2182,7 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2223,7 +2223,7 @@
         <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>9</v>
@@ -2300,7 +2300,7 @@
         <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -2377,7 +2377,7 @@
         <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>9</v>
@@ -2454,7 +2454,7 @@
         <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -2608,7 +2608,7 @@
         <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>9</v>
@@ -2839,7 +2839,7 @@
         <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>6</v>
@@ -2875,7 +2875,7 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -2943,25 +2943,25 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>69.23</v>
+        <v>53.85</v>
       </c>
       <c r="G2">
-        <v>26.92</v>
+        <v>46.15</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3131,7 +3131,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3166,36 +3166,16 @@
         <v>57</v>
       </c>
       <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
         <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>61</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920236</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -3237,10 +3217,10 @@
         <v>57</v>
       </c>
       <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
         <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>61</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3248,27 +3228,27 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920236</v>
+        <v>19330051920223</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920223</v>
+        <v>19330051920430</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
         <v>86</v>
@@ -3282,10 +3262,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920430</v>
+        <v>19330051920225</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
         <v>87</v>
@@ -3299,10 +3279,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920225</v>
+        <v>19330051920226</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
         <v>88</v>
@@ -3316,10 +3296,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920226</v>
+        <v>19330051920227</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
         <v>89</v>
@@ -3333,13 +3313,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920227</v>
+        <v>19330051920229</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
         <v>107</v>
@@ -3350,13 +3330,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920229</v>
+        <v>19330051920230</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
         <v>108</v>
@@ -3367,13 +3347,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920230</v>
+        <v>19330051920231</v>
       </c>
       <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
         <v>69</v>
-      </c>
-      <c r="C10" t="s">
-        <v>91</v>
       </c>
       <c r="D10" t="s">
         <v>109</v>
@@ -3384,13 +3364,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920231</v>
+        <v>19330051920232</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
         <v>110</v>
@@ -3401,10 +3381,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920232</v>
+        <v>19330051920233</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
         <v>92</v>
@@ -3418,10 +3398,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920233</v>
+        <v>19330051920234</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
         <v>93</v>
@@ -3435,10 +3415,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920234</v>
+        <v>19330051920429</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
         <v>94</v>
@@ -3452,13 +3432,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920429</v>
+        <v>19330051920235</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>114</v>
@@ -3469,13 +3449,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920235</v>
+        <v>19330051920236</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
         <v>115</v>
@@ -3489,10 +3469,10 @@
         <v>19330051920237</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
         <v>116</v>
@@ -3506,10 +3486,10 @@
         <v>19330051920228</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
         <v>117</v>
@@ -3523,10 +3503,10 @@
         <v>19330051420227</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
         <v>118</v>
@@ -3540,10 +3520,10 @@
         <v>19330051920404</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
         <v>119</v>
@@ -3557,10 +3537,10 @@
         <v>19330051920240</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
         <v>120</v>
@@ -3574,10 +3554,10 @@
         <v>19330051920239</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
         <v>121</v>
@@ -3591,10 +3571,10 @@
         <v>19330051920241</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
         <v>122</v>
@@ -3608,10 +3588,10 @@
         <v>19330051920242</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
         <v>123</v>
@@ -3625,10 +3605,10 @@
         <v>19330051920243</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s">
         <v>124</v>
@@ -3642,10 +3622,10 @@
         <v>19330051920244</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
         <v>125</v>
@@ -3659,10 +3639,10 @@
         <v>19330051920245</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
         <v>126</v>
@@ -3678,7 +3658,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3710,16 +3690,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920237</v>
+        <v>19330051920235</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -3733,22 +3713,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920237</v>
+        <v>19330051920235</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3756,22 +3736,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920234</v>
+        <v>19330051920430</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3779,22 +3759,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920429</v>
+        <v>19330051920234</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3802,22 +3782,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920235</v>
+        <v>19330051920429</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3828,10 +3808,10 @@
         <v>19330051920244</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
         <v>125</v>
@@ -3843,6 +3823,29 @@
         <v>47</v>
       </c>
       <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920245</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APM - Estadisticos 20211.xlsx
+++ b/grupos/5APM - Estadisticos 20211.xlsx
@@ -164,21 +164,21 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -191,145 +191,145 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALEJO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>CESPEDES</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>CHORA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>GARIBAY</t>
+  </si>
+  <si>
+    <t>GASPAR</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERAS</t>
+  </si>
+  <si>
+    <t>LADINO</t>
+  </si>
+  <si>
+    <t>LICEA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>SILVESTRE</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>CELICEO</t>
+  </si>
+  <si>
+    <t>CALPULALPAN</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ALCARAZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LLAVE</t>
+  </si>
+  <si>
+    <t>RAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
     <t>MOISES URIEL</t>
-  </si>
-  <si>
-    <t>ALEJO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CESPEDES</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>CHORA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>GARIBAY</t>
-  </si>
-  <si>
-    <t>GASPAR</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERAS</t>
-  </si>
-  <si>
-    <t>LADINO</t>
-  </si>
-  <si>
-    <t>LICEA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CELICEO</t>
-  </si>
-  <si>
-    <t>CALPULALPAN</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ALCARAZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
-    <t>RAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
   </si>
   <si>
     <t>ERICK MANUEL</t>
@@ -920,31 +920,31 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -997,22 +997,22 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>6</v>
@@ -1030,7 +1030,7 @@
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1038,7 +1038,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -1056,7 +1056,7 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -1065,7 +1065,7 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1074,31 +1074,31 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -1151,34 +1151,34 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>7</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>7</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1228,22 +1228,22 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1255,7 +1255,7 @@
         <v>6</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1305,25 +1305,25 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1332,7 +1332,7 @@
         <v>6</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>6</v>
@@ -1382,34 +1382,34 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>7</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1459,34 +1459,34 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>7</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>8</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1536,40 +1536,40 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>7</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>7</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1613,31 +1613,31 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1646,7 +1646,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1690,28 +1690,28 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1767,22 +1767,22 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>6</v>
@@ -1791,7 +1791,7 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1800,7 +1800,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1844,31 +1844,31 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1921,25 +1921,25 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -1998,28 +1998,28 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -2031,7 +2031,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2060,7 +2060,7 @@
         <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>6</v>
@@ -2075,34 +2075,34 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>6</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>5</v>
@@ -2152,31 +2152,31 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2229,34 +2229,34 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2306,22 +2306,22 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2333,7 +2333,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2383,28 +2383,28 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2460,28 +2460,28 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>9</v>
@@ -2522,7 +2522,7 @@
         <v>7</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>5</v>
@@ -2537,22 +2537,22 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>6</v>
@@ -2561,16 +2561,16 @@
         <v>5</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2614,34 +2614,34 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>7</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>7</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2676,13 +2676,13 @@
         <v>7</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -2691,22 +2691,22 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>6</v>
@@ -2715,7 +2715,7 @@
         <v>5</v>
       </c>
       <c r="V27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>5</v>
@@ -2724,7 +2724,7 @@
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2768,25 +2768,25 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>6</v>
@@ -2845,28 +2845,28 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -2878,7 +2878,7 @@
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2966,7 +2966,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
@@ -2975,19 +2975,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>73.08</v>
+        <v>84.62</v>
       </c>
       <c r="G3">
-        <v>26.92</v>
+        <v>15.38</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
@@ -3007,30 +3007,30 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>80.77</v>
+        <v>84.62</v>
       </c>
       <c r="G4">
         <v>15.38</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>50</v>
@@ -3039,19 +3039,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>84.62</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="G5">
-        <v>15.38</v>
+        <v>3.85</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3071,19 +3071,19 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>88.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>11.54</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3094,7 +3094,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
@@ -3103,19 +3103,19 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>92.31</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>7.69</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3131,7 +3131,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3156,26 +3156,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920224</v>
-      </c>
-      <c r="B2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3211,30 +3191,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920224</v>
+        <v>19330051920223</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920223</v>
+        <v>19330051920430</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
         <v>102</v>
@@ -3245,13 +3225,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920430</v>
+        <v>19330051920224</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
         <v>103</v>
@@ -3265,10 +3245,10 @@
         <v>19330051920225</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
         <v>104</v>
@@ -3282,10 +3262,10 @@
         <v>19330051920226</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
         <v>105</v>
@@ -3299,10 +3279,10 @@
         <v>19330051920227</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
         <v>106</v>
@@ -3316,10 +3296,10 @@
         <v>19330051920229</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
         <v>107</v>
@@ -3333,10 +3313,10 @@
         <v>19330051920230</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
         <v>108</v>
@@ -3350,10 +3330,10 @@
         <v>19330051920231</v>
       </c>
       <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
         <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>69</v>
       </c>
       <c r="D10" t="s">
         <v>109</v>
@@ -3367,10 +3347,10 @@
         <v>19330051920232</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
         <v>110</v>
@@ -3384,10 +3364,10 @@
         <v>19330051920233</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
         <v>111</v>
@@ -3401,10 +3381,10 @@
         <v>19330051920234</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
         <v>112</v>
@@ -3418,10 +3398,10 @@
         <v>19330051920429</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
         <v>113</v>
@@ -3435,10 +3415,10 @@
         <v>19330051920235</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
         <v>114</v>
@@ -3452,10 +3432,10 @@
         <v>19330051920236</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
         <v>115</v>
@@ -3469,10 +3449,10 @@
         <v>19330051920237</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
         <v>116</v>
@@ -3486,10 +3466,10 @@
         <v>19330051920228</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
         <v>117</v>
@@ -3503,10 +3483,10 @@
         <v>19330051420227</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
         <v>118</v>
@@ -3520,10 +3500,10 @@
         <v>19330051920404</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
         <v>119</v>
@@ -3537,10 +3517,10 @@
         <v>19330051920240</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
         <v>120</v>
@@ -3554,10 +3534,10 @@
         <v>19330051920239</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
         <v>121</v>
@@ -3571,10 +3551,10 @@
         <v>19330051920241</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s">
         <v>122</v>
@@ -3588,10 +3568,10 @@
         <v>19330051920242</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s">
         <v>123</v>
@@ -3605,10 +3585,10 @@
         <v>19330051920243</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
         <v>124</v>
@@ -3622,10 +3602,10 @@
         <v>19330051920244</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
         <v>125</v>
@@ -3639,10 +3619,10 @@
         <v>19330051920245</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
         <v>126</v>
@@ -3658,7 +3638,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3690,22 +3670,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920235</v>
+        <v>19330051920430</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3713,16 +3693,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920235</v>
+        <v>19330051920233</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -3736,16 +3716,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920430</v>
+        <v>19330051920429</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -3759,22 +3739,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920234</v>
+        <v>19330051920235</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3782,16 +3762,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920429</v>
+        <v>19330051920236</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -3805,16 +3785,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920244</v>
+        <v>19330051920237</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -3828,16 +3808,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920245</v>
+        <v>19330051920244</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -3846,6 +3826,29 @@
         <v>47</v>
       </c>
       <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920245</v>
+      </c>
+      <c r="B9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APM - Estadisticos 20211.xlsx
+++ b/grupos/5APM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="127">
   <si>
     <t>Materia</t>
   </si>
@@ -932,7 +932,7 @@
         <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>7</v>
@@ -1009,7 +1009,7 @@
         <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>7</v>
@@ -1027,7 +1027,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -1068,7 +1068,7 @@
         <v>5</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -1086,7 +1086,7 @@
         <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
         <v>6</v>
@@ -1163,7 +1163,7 @@
         <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -1240,7 +1240,7 @@
         <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>10</v>
@@ -1317,7 +1317,7 @@
         <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>9</v>
@@ -1394,7 +1394,7 @@
         <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>7</v>
@@ -1412,7 +1412,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1471,7 +1471,7 @@
         <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
         <v>7</v>
@@ -1548,7 +1548,7 @@
         <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>8</v>
@@ -1607,7 +1607,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -1625,7 +1625,7 @@
         <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
         <v>8</v>
@@ -1702,7 +1702,7 @@
         <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>8</v>
@@ -1761,7 +1761,7 @@
         <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -1779,7 +1779,7 @@
         <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
         <v>8</v>
@@ -1856,7 +1856,7 @@
         <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>10</v>
@@ -1933,7 +1933,7 @@
         <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>6</v>
@@ -1951,7 +1951,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -1992,7 +1992,7 @@
         <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>7</v>
@@ -2010,7 +2010,7 @@
         <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>6</v>
@@ -2028,7 +2028,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2069,7 +2069,7 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>6</v>
@@ -2087,7 +2087,7 @@
         <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>6</v>
@@ -2164,7 +2164,7 @@
         <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>6</v>
@@ -2182,7 +2182,7 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2241,7 +2241,7 @@
         <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
         <v>8</v>
@@ -2259,7 +2259,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2318,7 +2318,7 @@
         <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>8</v>
@@ -2395,7 +2395,7 @@
         <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>9</v>
@@ -2472,7 +2472,7 @@
         <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
         <v>8</v>
@@ -2531,7 +2531,7 @@
         <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>7</v>
@@ -2549,7 +2549,7 @@
         <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
         <v>6</v>
@@ -2626,7 +2626,7 @@
         <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>9</v>
@@ -2685,7 +2685,7 @@
         <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -2703,7 +2703,7 @@
         <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
         <v>8</v>
@@ -2762,7 +2762,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>6</v>
@@ -2780,7 +2780,7 @@
         <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
         <v>7</v>
@@ -2798,7 +2798,7 @@
         <v>6</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -2857,7 +2857,7 @@
         <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
         <v>8</v>
@@ -2875,7 +2875,7 @@
         <v>7</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2943,19 +2943,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>53.85</v>
+        <v>76.92</v>
       </c>
       <c r="G2">
-        <v>46.15</v>
+        <v>23.08</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3638,7 +3638,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3670,16 +3670,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920430</v>
+        <v>19330051920233</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -3693,16 +3693,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920233</v>
+        <v>19330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -3711,144 +3711,6 @@
         <v>47</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920429</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920235</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920236</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920237</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920244</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920245</v>
-      </c>
-      <c r="B9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>
